--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456797</v>
+        <v>121456820</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580647</v>
+        <v>580652</v>
       </c>
       <c r="R2" t="n">
-        <v>6386360</v>
+        <v>6386333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,13 +761,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456820</v>
+        <v>121456797</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +917,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580652</v>
+        <v>580647</v>
       </c>
       <c r="R4" t="n">
-        <v>6386333</v>
+        <v>6386360</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,17 +995,13 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456820</v>
+        <v>121456777</v>
       </c>
       <c r="B2" t="n">
         <v>57367</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580652</v>
+        <v>580625</v>
       </c>
       <c r="R2" t="n">
-        <v>6386333</v>
+        <v>6386246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121456777</v>
+        <v>121456797</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580625</v>
+        <v>580647</v>
       </c>
       <c r="R3" t="n">
-        <v>6386246</v>
+        <v>6386360</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,17 +880,13 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456797</v>
+        <v>121456820</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580647</v>
+        <v>580652</v>
       </c>
       <c r="R4" t="n">
-        <v>6386360</v>
+        <v>6386333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,13 +991,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456777</v>
+        <v>121456820</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580625</v>
+        <v>580652</v>
       </c>
       <c r="R2" t="n">
-        <v>6386246</v>
+        <v>6386333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121456797</v>
+        <v>121456777</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580647</v>
+        <v>580625</v>
       </c>
       <c r="R3" t="n">
-        <v>6386360</v>
+        <v>6386246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,13 +876,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456820</v>
+        <v>121456797</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +917,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580652</v>
+        <v>580647</v>
       </c>
       <c r="R4" t="n">
-        <v>6386333</v>
+        <v>6386360</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,17 +995,13 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121456820</v>
       </c>
       <c r="B2" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>121456777</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>121456797</v>
       </c>
       <c r="B4" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456820</v>
+        <v>121456797</v>
       </c>
       <c r="B2" t="n">
-        <v>57371</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580652</v>
+        <v>580647</v>
       </c>
       <c r="R2" t="n">
-        <v>6386333</v>
+        <v>6386360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +765,13 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,7 +793,7 @@
         <v>121456777</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456797</v>
+        <v>121456820</v>
       </c>
       <c r="B4" t="n">
-        <v>98104</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580647</v>
+        <v>580652</v>
       </c>
       <c r="R4" t="n">
-        <v>6386360</v>
+        <v>6386333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,13 +991,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456797</v>
+        <v>121456820</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580647</v>
+        <v>580652</v>
       </c>
       <c r="R2" t="n">
-        <v>6386360</v>
+        <v>6386333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,13 +761,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121456777</v>
+        <v>121456797</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +802,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580625</v>
+        <v>580647</v>
       </c>
       <c r="R3" t="n">
-        <v>6386246</v>
+        <v>6386360</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,17 +880,13 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456820</v>
+        <v>121456777</v>
       </c>
       <c r="B4" t="n">
         <v>57372</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580652</v>
+        <v>580625</v>
       </c>
       <c r="R4" t="n">
-        <v>6386333</v>
+        <v>6386246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456820</v>
+        <v>121456777</v>
       </c>
       <c r="B2" t="n">
         <v>57372</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580652</v>
+        <v>580625</v>
       </c>
       <c r="R2" t="n">
-        <v>6386333</v>
+        <v>6386246</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456777</v>
+        <v>121456820</v>
       </c>
       <c r="B4" t="n">
         <v>57372</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580625</v>
+        <v>580652</v>
       </c>
       <c r="R4" t="n">
-        <v>6386246</v>
+        <v>6386333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456777</v>
+        <v>121456797</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580625</v>
+        <v>580647</v>
       </c>
       <c r="R2" t="n">
-        <v>6386246</v>
+        <v>6386360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +765,13 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121456797</v>
+        <v>121456820</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580647</v>
+        <v>580652</v>
       </c>
       <c r="R3" t="n">
-        <v>6386360</v>
+        <v>6386333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,13 +876,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456820</v>
+        <v>121456777</v>
       </c>
       <c r="B4" t="n">
         <v>57372</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580652</v>
+        <v>580625</v>
       </c>
       <c r="R4" t="n">
-        <v>6386333</v>
+        <v>6386246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456797</v>
+        <v>121456820</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580647</v>
+        <v>580652</v>
       </c>
       <c r="R2" t="n">
-        <v>6386360</v>
+        <v>6386333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,13 +761,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121456820</v>
+        <v>121456777</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>580652</v>
+        <v>580625</v>
       </c>
       <c r="R3" t="n">
-        <v>6386333</v>
+        <v>6386246</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456777</v>
+        <v>121456797</v>
       </c>
       <c r="B4" t="n">
-        <v>57372</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,35 +917,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580625</v>
+        <v>580647</v>
       </c>
       <c r="R4" t="n">
-        <v>6386246</v>
+        <v>6386360</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,17 +995,13 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 56036-2024 artfynd.xlsx
+++ b/artfynd/A 56036-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121456777</v>
+        <v>121456797</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580625</v>
+        <v>580647</v>
       </c>
       <c r="R2" t="n">
-        <v>6386246</v>
+        <v>6386360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +765,13 @@
           <t>2024-12-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat låga</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121456797</v>
+        <v>121456777</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580647</v>
+        <v>580625</v>
       </c>
       <c r="R4" t="n">
-        <v>6386360</v>
+        <v>6386246</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,13 +991,17 @@
           <t>2024-12-03</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bearbetat låga</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
